--- a/InputData/hydgn/SoHPCCbRIC/Share of Hydrogen Production Capital Costs by Recipient ISIC Code.xlsx
+++ b/InputData/hydgn/SoHPCCbRIC/Share of Hydrogen Production Capital Costs by Recipient ISIC Code.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\hydgn\SoHPCCbRIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/hydgn/SoHPCCbRIC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6A2DD0-3A6E-49DF-9F0E-7A230114D7FB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{DB6A2DD0-3A6E-49DF-9F0E-7A230114D7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51800F92-BA63-406E-9963-3BAE1CA47035}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="105" windowWidth="25665" windowHeight="16830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="1080" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="3" r:id="rId2"/>
     <sheet name="SoHPCCbRIC" sheetId="2" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <definedNames>
     <definedName name="CEPCIinflator">Data!$C$11</definedName>
     <definedName name="CPIinflator">Data!$C$12</definedName>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="149">
   <si>
     <t>ISIC 01T03</t>
   </si>
@@ -147,9 +150,6 @@
     <t>biomass gasification</t>
   </si>
   <si>
-    <t>thermochemical water splitting</t>
-  </si>
-  <si>
     <t>Capital Costs</t>
   </si>
   <si>
@@ -481,6 +481,15 @@
   </si>
   <si>
     <t>Water and waste</t>
+  </si>
+  <si>
+    <t>hydrocarbon partial oxidation</t>
+  </si>
+  <si>
+    <t>electrolysis with guaranteed clean electricity</t>
+  </si>
+  <si>
+    <t>natural gas reforming with CCS</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1118,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1124,11 +1133,11 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1140,13 +1149,13 @@
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1255,7 +1264,6 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1263,8 +1271,8 @@
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1272,8 +1280,8 @@
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1282,14 +1290,14 @@
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1586,6 +1594,324 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="Data"/>
+      <sheetName val="SoHPCCbRIC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="10">
+          <cell r="L10">
+            <v>68084000</v>
+          </cell>
+          <cell r="M10" t="str">
+            <v>ISIC 28</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="L12">
+            <v>49148000</v>
+          </cell>
+          <cell r="M12" t="str">
+            <v>ISIC 41T43</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="L16">
+            <v>3658000</v>
+          </cell>
+          <cell r="M16" t="str">
+            <v>ISIC 28</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="L18">
+            <v>21570000</v>
+          </cell>
+          <cell r="M18" t="str">
+            <v>ISIC 41T43</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="L21">
+            <v>28492000</v>
+          </cell>
+          <cell r="M21" t="str">
+            <v>ISIC 64T66</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="I47" t="str">
+            <v>ISIC 28</v>
+          </cell>
+          <cell r="J47">
+            <v>0.4196428571428571</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="I49" t="str">
+            <v>ISIC 28</v>
+          </cell>
+          <cell r="J49">
+            <v>8.0357142857142849E-2</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="I50" t="str">
+            <v>ISIC 28</v>
+          </cell>
+          <cell r="J50">
+            <v>2.6785714285714284E-2</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="I51" t="str">
+            <v>ISIC 28</v>
+          </cell>
+          <cell r="J51">
+            <v>4.4642857142857137E-2</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="I52" t="str">
+            <v>ISIC 28</v>
+          </cell>
+          <cell r="J52">
+            <v>4.4642857142857137E-2</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="I53" t="str">
+            <v>ISIC 27</v>
+          </cell>
+          <cell r="J53">
+            <v>0.1875</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="I54" t="str">
+            <v>ISIC 27</v>
+          </cell>
+          <cell r="J54">
+            <v>1.7857142857142856E-2</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="I55" t="str">
+            <v>ISIC 28</v>
+          </cell>
+          <cell r="J55">
+            <v>4.4642857142857137E-2</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="I56" t="str">
+            <v>ISIC 28</v>
+          </cell>
+          <cell r="J56">
+            <v>8.9285714285714281E-3</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="I57" t="str">
+            <v>ISIC 41T43</v>
+          </cell>
+          <cell r="J57">
+            <v>1.7857142857142856E-2</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="I58" t="str">
+            <v>ISIC 41T43</v>
+          </cell>
+          <cell r="J58">
+            <v>0.10714285714285701</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="K86">
+            <v>1088450000</v>
+          </cell>
+          <cell r="L86" t="str">
+            <v>ISIC 28</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="K87">
+            <v>483000000</v>
+          </cell>
+          <cell r="L87" t="str">
+            <v>ISIC 41T43</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="K90">
+            <v>87900000</v>
+          </cell>
+          <cell r="L90" t="str">
+            <v>ISIC 28</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="K92">
+            <v>250600000</v>
+          </cell>
+          <cell r="L92" t="str">
+            <v>ISIC 41T43</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="K95">
+            <v>191000000</v>
+          </cell>
+          <cell r="L95" t="str">
+            <v>ISIC 64T66</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>ISIC 01T03</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>ISIC 05</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>ISIC 06</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>ISIC 07T08</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>ISIC 09</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>ISIC 10T12</v>
+          </cell>
+          <cell r="H1" t="str">
+            <v>ISIC 13T15</v>
+          </cell>
+          <cell r="I1" t="str">
+            <v>ISIC 16</v>
+          </cell>
+          <cell r="J1" t="str">
+            <v>ISIC 17T18</v>
+          </cell>
+          <cell r="K1" t="str">
+            <v>ISIC 19</v>
+          </cell>
+          <cell r="L1" t="str">
+            <v>ISIC 20</v>
+          </cell>
+          <cell r="M1" t="str">
+            <v>ISIC 21</v>
+          </cell>
+          <cell r="N1" t="str">
+            <v>ISIC 22</v>
+          </cell>
+          <cell r="O1" t="str">
+            <v>ISIC 231</v>
+          </cell>
+          <cell r="P1" t="str">
+            <v>ISIC 239</v>
+          </cell>
+          <cell r="Q1" t="str">
+            <v>ISIC 241</v>
+          </cell>
+          <cell r="R1" t="str">
+            <v>ISIC 242</v>
+          </cell>
+          <cell r="S1" t="str">
+            <v>ISIC 25</v>
+          </cell>
+          <cell r="T1" t="str">
+            <v>ISIC 26</v>
+          </cell>
+          <cell r="U1" t="str">
+            <v>ISIC 27</v>
+          </cell>
+          <cell r="V1" t="str">
+            <v>ISIC 28</v>
+          </cell>
+          <cell r="W1" t="str">
+            <v>ISIC 29</v>
+          </cell>
+          <cell r="X1" t="str">
+            <v>ISIC 30</v>
+          </cell>
+          <cell r="Y1" t="str">
+            <v>ISIC 31T33</v>
+          </cell>
+          <cell r="Z1" t="str">
+            <v>ISIC 351</v>
+          </cell>
+          <cell r="AA1" t="str">
+            <v>ISIC 352T353</v>
+          </cell>
+          <cell r="AB1" t="str">
+            <v>ISIC 36T39</v>
+          </cell>
+          <cell r="AC1" t="str">
+            <v>ISIC 41T43</v>
+          </cell>
+          <cell r="AD1" t="str">
+            <v>ISIC 45T47</v>
+          </cell>
+          <cell r="AE1" t="str">
+            <v>ISIC 49T53</v>
+          </cell>
+          <cell r="AF1" t="str">
+            <v>ISIC 55T56</v>
+          </cell>
+          <cell r="AG1" t="str">
+            <v>ISIC 58T60</v>
+          </cell>
+          <cell r="AH1" t="str">
+            <v>ISIC 61</v>
+          </cell>
+          <cell r="AI1" t="str">
+            <v>ISIC 62T63</v>
+          </cell>
+          <cell r="AJ1" t="str">
+            <v>ISIC 64T66</v>
+          </cell>
+          <cell r="AK1" t="str">
+            <v>ISIC 68</v>
+          </cell>
+          <cell r="AL1" t="str">
+            <v>ISIC 69T82</v>
+          </cell>
+          <cell r="AM1" t="str">
+            <v>ISIC 84</v>
+          </cell>
+          <cell r="AN1" t="str">
+            <v>ISIC 85</v>
+          </cell>
+          <cell r="AO1" t="str">
+            <v>ISIC 86T88</v>
+          </cell>
+          <cell r="AP1" t="str">
+            <v>ISIC 90T96</v>
+          </cell>
+          <cell r="AQ1" t="str">
+            <v>ISIC 97T98</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1850,147 +2176,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="65.140625" customWidth="1"/>
+    <col min="2" max="2" width="65.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="44" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="43">
         <v>2018</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="42" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="42" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="44" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="44" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="43">
         <v>2017</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="42" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="42" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B17" s="44" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B19" s="43">
         <v>2014</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B21" s="42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B22" s="45" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B22" s="45" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2007,17 +2333,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B10:N98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="99.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="99.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L10" s="48">
         <v>68084000</v>
       </c>
@@ -2025,10 +2351,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L11" s="48"/>
     </row>
-    <row r="12" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L12" s="48">
         <v>49148000</v>
       </c>
@@ -2036,16 +2362,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L13" s="48"/>
     </row>
-    <row r="14" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L14" s="48"/>
     </row>
-    <row r="15" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L15" s="48"/>
     </row>
-    <row r="16" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L16" s="48">
         <v>3658000</v>
       </c>
@@ -2053,10 +2379,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L17" s="48"/>
     </row>
-    <row r="18" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L18" s="48">
         <v>21570000</v>
       </c>
@@ -2064,13 +2390,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L19" s="48"/>
     </row>
-    <row r="20" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L20" s="48"/>
     </row>
-    <row r="21" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L21" s="48">
         <v>28492000</v>
       </c>
@@ -2078,136 +2404,136 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="2:14" ht="22.5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:14" ht="22" x14ac:dyDescent="0.65">
       <c r="B33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+    </row>
+    <row r="35" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C35" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="55"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="F34" s="55"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="55"/>
-    </row>
-    <row r="35" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C35" s="3" t="s">
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+    </row>
+    <row r="36" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="55"/>
-    </row>
-    <row r="36" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C36" s="3"/>
-    </row>
-    <row r="37" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="3"/>
-    </row>
-    <row r="38" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="C38" s="5">
         <v>50000</v>
       </c>
-      <c r="D38" s="56" t="s">
+      <c r="D38" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="57"/>
+    </row>
+    <row r="39" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D39" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="58"/>
-    </row>
-    <row r="39" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="59" t="s">
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B40" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="E39" s="53"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53"/>
-      <c r="H39" s="53"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B40" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="C40" s="7">
         <v>2012</v>
       </c>
-      <c r="D40" s="60"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="62"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D40" s="59"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="61"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B41" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="8">
         <v>2010</v>
       </c>
-      <c r="D41" s="63"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="65"/>
-    </row>
-    <row r="42" spans="2:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="62"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="64"/>
+    </row>
+    <row r="42" spans="2:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C42" s="9">
         <v>0.94218268901813196</v>
       </c>
-      <c r="D42" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="65"/>
+      <c r="D42" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="64"/>
       <c r="M42" t="s">
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C43" s="10">
         <v>1.100724186648488</v>
       </c>
-      <c r="D43" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="E43" s="53"/>
-      <c r="F43" s="53"/>
-      <c r="G43" s="53"/>
-      <c r="H43" s="54"/>
+      <c r="D43" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="53"/>
       <c r="M43" t="s">
+        <v>128</v>
+      </c>
+      <c r="N43" t="s">
         <v>129</v>
       </c>
-      <c r="N43" t="s">
+    </row>
+    <row r="44" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M44" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M44" t="s">
+      <c r="N44" t="s">
         <v>131</v>
       </c>
-      <c r="N44" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B45" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
@@ -2219,41 +2545,41 @@
         <v>1</v>
       </c>
       <c r="N45" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" ht="53.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" ht="53.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B46" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E46" s="15" t="s">
+      <c r="F46" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F46" s="16" t="s">
+      <c r="G46" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H46" s="17" t="s">
         <v>47</v>
-      </c>
-      <c r="G46" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="H46" s="17" t="s">
-        <v>48</v>
       </c>
       <c r="M46" t="s">
         <v>2</v>
       </c>
       <c r="N46" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B47" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="19">
         <v>47851875</v>
@@ -2280,12 +2606,12 @@
         <v>3</v>
       </c>
       <c r="N47" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B48" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" s="25"/>
       <c r="D48" s="20">
@@ -2304,12 +2630,12 @@
         <v>4</v>
       </c>
       <c r="N48" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B49" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C49" s="25">
         <v>9163125</v>
@@ -2336,12 +2662,12 @@
         <v>5</v>
       </c>
       <c r="N49" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B50" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="25">
         <v>3054375</v>
@@ -2368,12 +2694,12 @@
         <v>6</v>
       </c>
       <c r="N50" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B51" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C51" s="25">
         <v>5090625</v>
@@ -2400,12 +2726,12 @@
         <v>7</v>
       </c>
       <c r="N51" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B52" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C52" s="25">
         <v>5090625</v>
@@ -2429,15 +2755,15 @@
         <v>4.4642857142857137E-2</v>
       </c>
       <c r="M52" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N52" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B53" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C53" s="25">
         <v>21380625</v>
@@ -2461,15 +2787,15 @@
         <v>0.1875</v>
       </c>
       <c r="M53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N53" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B54" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C54" s="25">
         <v>2036250</v>
@@ -2496,12 +2822,12 @@
         <v>8</v>
       </c>
       <c r="N54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B55" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C55" s="25">
         <v>5090625</v>
@@ -2525,15 +2851,15 @@
         <v>4.4642857142857137E-2</v>
       </c>
       <c r="M55" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B56" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C56" s="25">
         <v>1018125</v>
@@ -2557,15 +2883,15 @@
         <v>8.9285714285714281E-3</v>
       </c>
       <c r="M56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N56" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B57" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C57" s="25">
         <v>2036250</v>
@@ -2589,13 +2915,13 @@
         <v>1.7857142857142856E-2</v>
       </c>
       <c r="M57" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N57" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="58" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B58" s="30"/>
       <c r="C58" s="31">
         <v>101812500</v>
@@ -2617,32 +2943,32 @@
         <v>0.10714285714285701</v>
       </c>
       <c r="M58" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N58" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="59" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C59" s="36"/>
       <c r="M59" t="s">
         <v>9</v>
       </c>
       <c r="N59" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14" x14ac:dyDescent="0.35">
       <c r="M60" t="s">
         <v>10</v>
       </c>
       <c r="N60" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B61" s="37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C61" s="37">
         <v>900</v>
@@ -2651,12 +2977,12 @@
         <v>11</v>
       </c>
       <c r="N61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B62" s="38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C62" s="37">
         <v>54.3</v>
@@ -2665,12 +2991,12 @@
         <v>12</v>
       </c>
       <c r="N62" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B63" s="38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C63" s="39">
         <v>113125</v>
@@ -2679,12 +3005,12 @@
         <v>13</v>
       </c>
       <c r="N63" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B64" s="37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C64" s="40">
         <v>0.47</v>
@@ -2693,12 +3019,12 @@
         <v>14</v>
       </c>
       <c r="N64" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B65" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C65" s="40">
         <v>0.53</v>
@@ -2707,54 +3033,54 @@
         <v>15</v>
       </c>
       <c r="N65" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B66" s="41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C66" s="40">
         <v>0.09</v>
       </c>
       <c r="M66" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N66" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B67" s="41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C67" s="40">
         <v>0.03</v>
       </c>
       <c r="M67" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N67" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B68" s="41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C68" s="40">
         <v>0.05</v>
       </c>
       <c r="M68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N68" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B69" s="41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C69" s="40">
         <v>0.05</v>
@@ -2763,12 +3089,12 @@
         <v>16</v>
       </c>
       <c r="N69" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B70" s="41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C70" s="40">
         <v>0.21</v>
@@ -2777,12 +3103,12 @@
         <v>17</v>
       </c>
       <c r="N70" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B71" s="41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C71" s="40">
         <v>0.02</v>
@@ -2791,12 +3117,12 @@
         <v>18</v>
       </c>
       <c r="N71" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B72" s="41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C72" s="40">
         <v>0.05</v>
@@ -2805,12 +3131,12 @@
         <v>19</v>
       </c>
       <c r="N72" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B73" s="41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C73" s="40">
         <v>0.01</v>
@@ -2819,12 +3145,12 @@
         <v>20</v>
       </c>
       <c r="N73" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B74" s="41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C74" s="40">
         <v>0.02</v>
@@ -2833,82 +3159,82 @@
         <v>21</v>
       </c>
       <c r="N74" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.35">
       <c r="M75" t="s">
         <v>22</v>
       </c>
       <c r="N75" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.35">
       <c r="M76" t="s">
         <v>23</v>
       </c>
       <c r="N76" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.35">
       <c r="M77" t="s">
         <v>24</v>
       </c>
       <c r="N77" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14" x14ac:dyDescent="0.35">
       <c r="M78" t="s">
         <v>25</v>
       </c>
       <c r="N78" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.35">
       <c r="M79" t="s">
         <v>26</v>
       </c>
       <c r="N79" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14" x14ac:dyDescent="0.35">
       <c r="M80" t="s">
         <v>27</v>
       </c>
       <c r="N80" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="81" spans="11:14" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="81" spans="11:14" x14ac:dyDescent="0.35">
       <c r="M81" t="s">
         <v>28</v>
       </c>
       <c r="N81" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="11:14" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="11:14" x14ac:dyDescent="0.35">
       <c r="M82" t="s">
         <v>29</v>
       </c>
       <c r="N82" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="83" spans="11:14" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="83" spans="11:14" x14ac:dyDescent="0.35">
       <c r="M83" t="s">
         <v>30</v>
       </c>
       <c r="N83" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="86" spans="11:14" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="86" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K86" s="48">
         <v>1088450000</v>
       </c>
@@ -2916,7 +3242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="11:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K87" s="48">
         <v>483000000</v>
       </c>
@@ -2924,13 +3250,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="11:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K88" s="48"/>
     </row>
-    <row r="89" spans="11:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K89" s="48"/>
     </row>
-    <row r="90" spans="11:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K90" s="48">
         <v>87900000</v>
       </c>
@@ -2938,10 +3264,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="11:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K91" s="48"/>
     </row>
-    <row r="92" spans="11:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K92" s="48">
         <v>250600000</v>
       </c>
@@ -2949,13 +3275,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="11:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K93" s="48"/>
     </row>
-    <row r="94" spans="11:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K94" s="48"/>
     </row>
-    <row r="95" spans="11:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K95" s="48">
         <v>191000000</v>
       </c>
@@ -2963,7 +3289,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="11:11" x14ac:dyDescent="0.35">
       <c r="K98" s="47">
         <f>SUM(K86:K95)</f>
         <v>2100950000</v>
@@ -2995,1008 +3321,1354 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:AQ6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AQ8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="26" width="10.7109375" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" customWidth="1"/>
-    <col min="28" max="43" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="26" width="10.7265625" customWidth="1"/>
+    <col min="27" max="27" width="13.1796875" customWidth="1"/>
+    <col min="28" max="43" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A1" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="E1" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="51" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="51" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="51" t="s">
+      <c r="M1" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="M1" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="N1" s="51" t="s">
+      <c r="N1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="51" t="s">
+      <c r="O1" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="P1" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="Q1" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="R1" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="R1" s="51" t="s">
+      <c r="S1" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="T1" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="U1" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="V1" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="W1" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="X1" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y1" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z1" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="S1" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="51" t="s">
-        <v>10</v>
-      </c>
-      <c r="U1" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="V1" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="W1" s="51" t="s">
-        <v>13</v>
-      </c>
-      <c r="X1" s="51" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y1" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z1" s="51" t="s">
+      <c r="AA1" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="AA1" s="51" t="s">
+      <c r="AB1" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="AB1" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="AC1" s="51" t="s">
+      <c r="AC1" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="AD1" s="51" t="s">
+      <c r="AD1" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="AE1" s="51" t="s">
+      <c r="AE1" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="AF1" s="51" t="s">
+      <c r="AF1" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="AG1" s="51" t="s">
+      <c r="AG1" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="AH1" s="51" t="s">
+      <c r="AH1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AI1" s="51" t="s">
+      <c r="AI1" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="AJ1" s="51" t="s">
+      <c r="AJ1" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="AK1" s="51" t="s">
+      <c r="AK1" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="AL1" s="51" t="s">
+      <c r="AL1" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="AM1" s="51" t="s">
+      <c r="AM1" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="AN1" s="51" t="s">
+      <c r="AN1" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AO1" s="51" t="s">
+      <c r="AO1" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="AP1" s="51" t="s">
+      <c r="AP1" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="AQ1" s="51" t="s">
+      <c r="AQ1" s="50" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,B1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,C1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,D1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,E1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,F1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,G1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,H1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,I1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,J1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,K1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="L2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,L1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,M1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="N2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,N1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="O2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,O1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="P2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,P1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="Q2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,Q1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="R2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,R1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="S2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,S1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="T2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,T1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="U2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,U1,Data!$J$47:$J$58)</f>
+      <c r="B2">
+        <f>SUMIF([1]Data!$I$47:$I$58,B1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <f>SUMIF([1]Data!$I$47:$I$58,C1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <f>SUMIF([1]Data!$I$47:$I$58,D1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>SUMIF([1]Data!$I$47:$I$58,E1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <f>SUMIF([1]Data!$I$47:$I$58,F1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>SUMIF([1]Data!$I$47:$I$58,G1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <f>SUMIF([1]Data!$I$47:$I$58,H1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <f>SUMIF([1]Data!$I$47:$I$58,I1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>SUMIF([1]Data!$I$47:$I$58,J1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>SUMIF([1]Data!$I$47:$I$58,K1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>SUMIF([1]Data!$I$47:$I$58,L1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <f>SUMIF([1]Data!$I$47:$I$58,M1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>SUMIF([1]Data!$I$47:$I$58,N1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>SUMIF([1]Data!$I$47:$I$58,O1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <f>SUMIF([1]Data!$I$47:$I$58,P1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>SUMIF([1]Data!$I$47:$I$58,Q1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>SUMIF([1]Data!$I$47:$I$58,R1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>SUMIF([1]Data!$I$47:$I$58,S1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>SUMIF([1]Data!$I$47:$I$58,T1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>SUMIF([1]Data!$I$47:$I$58,U1,[1]Data!$J$47:$J$58)</f>
         <v>0.20535714285714285</v>
       </c>
-      <c r="V2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,V1,Data!$J$47:$J$58)</f>
+      <c r="V2">
+        <f>SUMIF([1]Data!$I$47:$I$58,V1,[1]Data!$J$47:$J$58)</f>
         <v>0.66964285714285687</v>
       </c>
-      <c r="W2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,W1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="X2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,X1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="Y2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,Y1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="Z2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,Z1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AA2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AA1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AB2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AB1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AC2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AC1,Data!$J$47:$J$58)</f>
+      <c r="W2">
+        <f>SUMIF([1]Data!$I$47:$I$58,W1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f>SUMIF([1]Data!$I$47:$I$58,X1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <f>SUMIF([1]Data!$I$47:$I$58,Y1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <f>SUMIF([1]Data!$I$47:$I$58,Z1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AA1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AB1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AC1,[1]Data!$J$47:$J$58)</f>
         <v>0.12499999999999986</v>
       </c>
-      <c r="AD2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AD1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AE2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AE1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AF2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AF1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AG2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AG1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AH2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AH1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AI2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AI1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AJ1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AK2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AK1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AL2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AL1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AM2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AM1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AN2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AN1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AO2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AO1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AP2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AP1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="50">
-        <f>SUMIF(Data!$I$47:$I$58,AQ1,Data!$J$47:$J$58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AD2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AD1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AE1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AF1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AG1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AH1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AI1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AJ1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AK1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AL1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AM1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AN1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AO1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AP1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f>SUMIF([1]Data!$I$47:$I$58,AQ1,[1]Data!$J$47:$J$58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!B1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!C1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!D1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!E1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!F1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!G1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!H1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!I1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!J1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!K1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!L1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!M1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!N1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!O1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="P3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!P1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!Q1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="R3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!R1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="S3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!S1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="T3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!T1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="U3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!U1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="V3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!V1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
+      <c r="B3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!B1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!C1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!D1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!E1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!F1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!G1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!H1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!I1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!J1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!K1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!L1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!M1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!N1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!O1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!P1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!Q1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!R1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!S1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!T1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!U1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!V1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
         <v>0.41966165941316863</v>
       </c>
-      <c r="W3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!W1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="X3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!X1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!Y1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="Z3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!Z1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AA3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AA1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AB3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AB1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AC3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AC1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
+      <c r="W3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!W1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!X1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!Y1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!Z1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AA1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AB1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AC1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
         <v>0.41367167392016474</v>
       </c>
-      <c r="AD3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AD1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AE3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AE1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AF3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AF1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AG3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AG1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AH3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AH1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AI3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AI1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AJ1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
+      <c r="AD3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AD1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AE1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AF1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AG1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AH1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AI1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AJ1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="AK3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AK1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AL3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AL1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AM3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AM1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AN3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AN1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AO3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AO1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AP3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AP1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="50">
-        <f>SUMIF(Data!$M$10:$M$21,SoHPCCbRIC!AQ1,Data!$L$10:$L$21)/SUM(Data!$L$10:$L$21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AK3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AK1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AL1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AM1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AN1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AO1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AP1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f>SUMIF([1]Data!$M$10:$M$21,[1]SoHPCCbRIC!AQ1,[1]Data!$L$10:$L$21)/SUM([1]Data!$L$10:$L$21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,B1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,C1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,D1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,E1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,F1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,G1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,H1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,I1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,J1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,K1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,L1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,M1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,N1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="O4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,O1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="P4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,P1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,Q1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="R4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,R1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="S4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,S1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="T4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,T1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="U4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,U1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="V4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,V1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
+      <c r="B4">
+        <f>SUMIF([1]Data!$L$86:$L$95,B1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <f>SUMIF([1]Data!$L$86:$L$95,C1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <f>SUMIF([1]Data!$L$86:$L$95,D1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f>SUMIF([1]Data!$L$86:$L$95,E1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>SUMIF([1]Data!$L$86:$L$95,F1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f>SUMIF([1]Data!$L$86:$L$95,G1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <f>SUMIF([1]Data!$L$86:$L$95,H1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <f>SUMIF([1]Data!$L$86:$L$95,I1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>SUMIF([1]Data!$L$86:$L$95,J1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <f>SUMIF([1]Data!$L$86:$L$95,K1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f>SUMIF([1]Data!$L$86:$L$95,L1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f>SUMIF([1]Data!$L$86:$L$95,M1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f>SUMIF([1]Data!$L$86:$L$95,N1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f>SUMIF([1]Data!$L$86:$L$95,O1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <f>SUMIF([1]Data!$L$86:$L$95,P1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <f>SUMIF([1]Data!$L$86:$L$95,Q1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <f>SUMIF([1]Data!$L$86:$L$95,R1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <f>SUMIF([1]Data!$L$86:$L$95,S1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <f>SUMIF([1]Data!$L$86:$L$95,T1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f>SUMIF([1]Data!$L$86:$L$95,U1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <f>SUMIF([1]Data!$L$86:$L$95,V1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
         <v>0.55991337252195439</v>
       </c>
-      <c r="W4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,W1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="X4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,X1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="Y4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,Y1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="Z4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,Z1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AA4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AA1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AB4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AB1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AC4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AC1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
+      <c r="W4">
+        <f>SUMIF([1]Data!$L$86:$L$95,W1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <f>SUMIF([1]Data!$L$86:$L$95,X1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <f>SUMIF([1]Data!$L$86:$L$95,Y1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <f>SUMIF([1]Data!$L$86:$L$95,Z1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AA1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AB1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AC1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
         <v>0.34917537304552704</v>
       </c>
-      <c r="AD4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AD1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AE4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AE1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AF4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AF1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AG4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AG1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AH4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AH1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AI4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AI1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AJ1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
+      <c r="AD4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AD1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AE1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AF1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AG1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AH1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AI1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AJ1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
         <v>9.0911254432518629E-2</v>
       </c>
-      <c r="AK4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AK1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AL4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AL1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AM4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AM1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AN4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AN1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AO4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AO1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AP4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AP1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="50">
-        <f>SUMIF(Data!$L$86:$L$95,AQ1,Data!$K$86:$K$95)/SUM(Data!$K$86:$K$95)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AK4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AK1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AL1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AM1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AN1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AO1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AP1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f>SUMIF([1]Data!$L$86:$L$95,AQ1,[1]Data!$K$86:$K$95)/SUM([1]Data!$K$86:$K$95)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="50">
+      <c r="B5">
         <f>B4</f>
         <v>0</v>
       </c>
-      <c r="C5" s="50">
+      <c r="C5">
         <f t="shared" ref="C5:AQ5" si="0">C4</f>
         <v>0</v>
       </c>
-      <c r="D5" s="50">
-        <f t="shared" ref="D5" si="1">D4</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="50">
+      <c r="D5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="50">
+      <c r="E5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G5" s="50">
+      <c r="F5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H5" s="50">
+      <c r="G5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="50">
+      <c r="H5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J5" s="50">
+      <c r="I5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K5" s="50">
+      <c r="J5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L5" s="50">
+      <c r="K5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M5" s="50">
-        <f t="shared" ref="M5" si="2">M4</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="50">
+      <c r="L5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O5" s="50">
+      <c r="M5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P5" s="50">
-        <f t="shared" ref="P5" si="3">P4</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="50">
+      <c r="N5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R5" s="50">
-        <f t="shared" ref="R5" si="4">R4</f>
-        <v>0</v>
-      </c>
-      <c r="S5" s="50">
+      <c r="O5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T5" s="50">
+      <c r="P5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U5" s="50">
+      <c r="Q5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V5" s="50">
+      <c r="R5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V5">
         <f t="shared" si="0"/>
         <v>0.55991337252195439</v>
       </c>
-      <c r="W5" s="50">
+      <c r="W5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X5" s="50">
+      <c r="X5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y5" s="50">
+      <c r="Y5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z5" s="50">
+      <c r="Z5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA5" s="50">
-        <f t="shared" ref="AA5:AB5" si="5">AA4</f>
-        <v>0</v>
-      </c>
-      <c r="AB5" s="50">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AC5" s="50">
+      <c r="AA5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC5">
         <f t="shared" si="0"/>
         <v>0.34917537304552704</v>
       </c>
-      <c r="AD5" s="50">
+      <c r="AD5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AE5" s="50">
+      <c r="AE5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF5" s="50">
+      <c r="AF5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AG5" s="50">
+      <c r="AG5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH5" s="50">
+      <c r="AH5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AI5" s="50">
+      <c r="AI5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AJ5" s="50">
+      <c r="AJ5">
         <f t="shared" si="0"/>
         <v>9.0911254432518629E-2</v>
       </c>
-      <c r="AK5" s="50">
+      <c r="AK5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AL5" s="50">
+      <c r="AL5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM5" s="50">
+      <c r="AM5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN5" s="50">
+      <c r="AN5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AO5" s="50">
+      <c r="AO5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AP5" s="50">
+      <c r="AP5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AQ5" s="50">
+      <c r="AQ5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="50">
-        <f>B4</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="50">
-        <f t="shared" ref="C6:AQ6" si="6">C4</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="50">
-        <f t="shared" ref="D6" si="7">D4</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="50">
-        <f t="shared" ref="M6" si="8">M4</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P6" s="50">
-        <f t="shared" ref="P6" si="9">P4</f>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R6" s="50">
-        <f t="shared" ref="R6" si="10">R4</f>
-        <v>0</v>
-      </c>
-      <c r="S6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V6" s="50">
-        <f t="shared" si="6"/>
-        <v>0.55991337252195439</v>
-      </c>
-      <c r="W6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA6" s="50">
-        <f t="shared" ref="AA6:AB6" si="11">AA4</f>
-        <v>0</v>
-      </c>
-      <c r="AB6" s="50">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AC6" s="50">
-        <f t="shared" si="6"/>
-        <v>0.34917537304552704</v>
-      </c>
-      <c r="AD6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AE6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AF6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AG6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AH6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AI6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="50">
-        <f t="shared" si="6"/>
-        <v>9.0911254432518629E-2</v>
-      </c>
-      <c r="AK6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AL6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AM6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AN6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AO6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AP6" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="50">
-        <f t="shared" si="6"/>
+        <v>146</v>
+      </c>
+      <c r="B6">
+        <f t="shared" ref="B6:U6" si="1">B3</f>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <f>V3</f>
+        <v>0.41966165941316863</v>
+      </c>
+      <c r="W6">
+        <f t="shared" ref="W6:AQ6" si="2">W3</f>
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="2"/>
+        <v>0.41367167392016474</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7">
+        <f>B2</f>
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:AQ8" si="3">C2</f>
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="3"/>
+        <v>0.20535714285714285</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="3"/>
+        <v>0.66964285714285687</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="3"/>
+        <v>0.12499999999999986</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8">
+        <f>B3</f>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="3"/>
+        <v>0.41966165941316863</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="3"/>
+        <v>0.41367167392016474</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="3"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4004,4 +4676,198 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
+    <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1659011e-6b88-4225-9a61-aaf33aaf19e8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37F78D41-AD51-4B2E-88D3-DB064F707CCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51403215-EB8D-418D-8335-3BE4BAF13163}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCF94D6E-5636-4110-ADB6-8B35E3CDFD49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>